--- a/artfynd/A 26977-2024 artfynd.xlsx
+++ b/artfynd/A 26977-2024 artfynd.xlsx
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Andreas Bernhold, Isak Vahlström</t>
+          <t>Isak Vahlström, Andreas Bernhold</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">

--- a/artfynd/A 26977-2024 artfynd.xlsx
+++ b/artfynd/A 26977-2024 artfynd.xlsx
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Andreas Bernhold</t>
+          <t>Andreas Bernhold, Isak Vahlström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">

--- a/artfynd/A 26977-2024 artfynd.xlsx
+++ b/artfynd/A 26977-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>124667496</v>
       </c>
       <c r="B2" t="n">
-        <v>79926</v>
+        <v>80063</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
